--- a/第四部分/忘川风华录_视频数据表格展示.xlsx
+++ b/第四部分/忘川风华录_视频数据表格展示.xlsx
@@ -1094,31 +1094,13 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
-      <color rgb="FF2C3E50"/>
-      <name val="Segoe UI"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
-      <color rgb="FF2C3E50"/>
-      <name val="宋体"/>
-      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -1466,40 +1448,12 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFDEE0E3"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFDEE0E3"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFDEE0E3"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFDEE0E3"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFDEE0E3"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFDEE0E3"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FFDEE0E3"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1635,137 +1589,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1775,19 +1729,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
@@ -2328,314 +2273,316 @@
   <sheetFormatPr defaultColWidth="9.81818181818182" defaultRowHeight="14" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="22.2727272727273" style="1" customWidth="1"/>
-    <col min="2" max="16384" width="9.81818181818182" style="1"/>
+    <col min="2" max="2" width="26.0909090909091" style="1" customWidth="1"/>
+    <col min="3" max="3" width="26.5454545454545" style="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.81818181818182" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="5" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="5" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="5" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="5" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="5" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="5" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="5" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="5" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="5" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" s="5" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="5" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C14" s="5" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="B15" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="5" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="B16" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="C16" s="5" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="17" spans="1:3">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="B17" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="C17" s="5" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18" s="8" t="s">
+      <c r="A18" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="B18" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C18" s="8" t="s">
+      <c r="C18" s="5" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="8" t="s">
+      <c r="A19" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B19" s="8" t="s">
+      <c r="B19" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="C19" s="5" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="20" spans="1:3">
-      <c r="A20" s="8" t="s">
+      <c r="A20" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="B20" s="8" t="s">
+      <c r="B20" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C20" s="8" t="s">
+      <c r="C20" s="5" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="21" spans="1:3">
-      <c r="A21" s="8" t="s">
+      <c r="A21" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="B21" s="8" t="s">
+      <c r="B21" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="C21" s="5" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="22" spans="1:3">
-      <c r="A22" s="8" t="s">
+      <c r="A22" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="B22" s="8" t="s">
+      <c r="B22" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C22" s="8" t="s">
+      <c r="C22" s="5" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="23" spans="1:3">
-      <c r="A23" s="8" t="s">
+      <c r="A23" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="B23" s="8" t="s">
+      <c r="B23" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C23" s="8" t="s">
+      <c r="C23" s="5" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="24" spans="1:3">
-      <c r="A24" s="8" t="s">
+      <c r="A24" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="B24" s="8" t="s">
+      <c r="B24" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C24" s="8" t="s">
+      <c r="C24" s="5" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="25" spans="1:3">
-      <c r="A25" s="8" t="s">
+      <c r="A25" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="B25" s="8" t="s">
+      <c r="B25" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C25" s="8" t="s">
+      <c r="C25" s="5" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="26" spans="1:3">
-      <c r="A26" s="8" t="s">
+      <c r="A26" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="B26" s="8" t="s">
+      <c r="B26" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C26" s="8" t="s">
+      <c r="C26" s="5" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:3">
-      <c r="A27" s="8" t="s">
+      <c r="A27" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="B27" s="8" t="s">
+      <c r="B27" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C27" s="8" t="s">
+      <c r="C27" s="5" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="28" spans="1:3">
-      <c r="A28" s="8" t="s">
+      <c r="A28" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="B28" s="8" t="s">
+      <c r="B28" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C28" s="8" t="s">
+      <c r="C28" s="5" t="s">
         <v>61</v>
       </c>
     </row>
@@ -2653,10 +2600,13 @@
   <cols>
     <col min="1" max="1" width="9.81818181818182" style="1" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="22.2727272727273" style="1" customWidth="1"/>
-    <col min="3" max="16384" width="9.81818181818182" style="1"/>
+    <col min="3" max="3" width="22.6363636363636" style="1" customWidth="1"/>
+    <col min="4" max="4" width="23.2727272727273" style="1" customWidth="1"/>
+    <col min="5" max="5" width="58.7272727272727" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.81818181818182" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.75" spans="1:5">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>62</v>
       </c>
@@ -2669,11 +2619,11 @@
       <c r="D1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="1" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="2" ht="14.75" spans="1:5">
+    <row r="2" spans="1:5">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -2686,11 +2636,11 @@
       <c r="D2" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="1" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="3" ht="17.75" spans="1:5">
+    <row r="3" spans="1:5">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -2700,14 +2650,14 @@
       <c r="C3" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="4" ht="17.75" spans="1:5">
+    <row r="4" spans="1:5">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -2717,14 +2667,14 @@
       <c r="C4" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="1" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="5" ht="17.75" spans="1:5">
+    <row r="5" spans="1:5">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -2734,14 +2684,14 @@
       <c r="C5" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="1" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="6" ht="17.75" spans="1:5">
+    <row r="6" spans="1:5">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -2751,14 +2701,14 @@
       <c r="C6" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="1" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="7" ht="17.75" spans="1:5">
+    <row r="7" spans="1:5">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -2768,14 +2718,14 @@
       <c r="C7" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="8" ht="17.75" spans="1:5">
+    <row r="8" spans="1:5">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -2785,14 +2735,14 @@
       <c r="C8" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="1" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="9" ht="17.75" spans="1:5">
+    <row r="9" spans="1:5">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -2802,14 +2752,14 @@
       <c r="C9" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="1" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="10" ht="17.75" spans="1:5">
+    <row r="10" spans="1:5">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -2819,31 +2769,31 @@
       <c r="C10" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="1" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="11" ht="14.75" spans="1:5">
+    <row r="11" ht="28" spans="1:5">
       <c r="A11" s="1">
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="3" t="s">
         <v>95</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="1" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="12" ht="17.75" spans="1:5">
+    <row r="12" spans="1:5">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -2853,14 +2803,14 @@
       <c r="C12" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D12" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="1" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="13" ht="17.75" spans="1:5">
+    <row r="13" spans="1:5">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -2870,14 +2820,14 @@
       <c r="C13" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D13" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E13" s="1" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="14" ht="17.75" spans="1:5">
+    <row r="14" spans="1:5">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -2887,14 +2837,14 @@
       <c r="C14" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="1" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="15" ht="17.75" spans="1:5">
+    <row r="15" spans="1:5">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -2904,14 +2854,14 @@
       <c r="C15" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="D15" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="E15" s="1" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="16" ht="14.75" spans="1:5">
+    <row r="16" spans="1:5">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -2924,11 +2874,11 @@
       <c r="D16" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E16" s="1" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="17" ht="14.75" spans="1:5">
+    <row r="17" spans="1:5">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -2941,11 +2891,11 @@
       <c r="D17" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="E17" s="4" t="s">
+      <c r="E17" s="1" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="18" ht="17.75" spans="1:5">
+    <row r="18" spans="1:5">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -2955,14 +2905,14 @@
       <c r="C18" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="D18" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="E18" s="4" t="s">
+      <c r="E18" s="1" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="19" ht="17.75" spans="1:5">
+    <row r="19" spans="1:5">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -2972,14 +2922,14 @@
       <c r="C19" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="D19" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="E19" s="4" t="s">
+      <c r="E19" s="1" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="20" ht="17.75" spans="1:5">
+    <row r="20" spans="1:5">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -2989,14 +2939,14 @@
       <c r="C20" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="D20" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="E20" s="4" t="s">
+      <c r="E20" s="1" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="21" ht="17.75" spans="1:5">
+    <row r="21" spans="1:5">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -3006,14 +2956,14 @@
       <c r="C21" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="D21" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="E21" s="4" t="s">
+      <c r="E21" s="1" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="22" ht="14.75" spans="1:5">
+    <row r="22" spans="1:5">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -3026,11 +2976,11 @@
       <c r="D22" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="E22" s="4" t="s">
+      <c r="E22" s="1" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="23" ht="17.75" spans="1:5">
+    <row r="23" spans="1:5">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -3040,14 +2990,14 @@
       <c r="C23" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="D23" s="5" t="s">
+      <c r="D23" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="E23" s="4" t="s">
+      <c r="E23" s="1" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="24" ht="14.75" spans="1:5">
+    <row r="24" spans="1:5">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -3057,14 +3007,14 @@
       <c r="C24" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="D24" s="6" t="s">
+      <c r="D24" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="E24" s="4" t="s">
+      <c r="E24" s="1" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="25" ht="17.75" spans="1:5">
+    <row r="25" spans="1:5">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -3074,14 +3024,14 @@
       <c r="C25" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="D25" s="5" t="s">
+      <c r="D25" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="E25" s="4" t="s">
+      <c r="E25" s="1" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="26" ht="17.75" spans="1:5">
+    <row r="26" spans="1:5">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -3091,14 +3041,14 @@
       <c r="C26" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="D26" s="5" t="s">
+      <c r="D26" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="E26" s="4" t="s">
+      <c r="E26" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="27" ht="14.75" spans="1:5">
+    <row r="27" spans="1:5">
       <c r="A27" s="1">
         <v>26</v>
       </c>
@@ -3108,14 +3058,14 @@
       <c r="C27" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="D27" s="6" t="s">
+      <c r="D27" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="E27" s="4" t="s">
+      <c r="E27" s="1" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="28" ht="14.75" spans="1:5">
+    <row r="28" spans="1:5">
       <c r="A28" s="1">
         <v>27</v>
       </c>
@@ -3128,11 +3078,11 @@
       <c r="D28" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="E28" s="4" t="s">
+      <c r="E28" s="1" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="29" ht="14.75" spans="1:5">
+    <row r="29" spans="1:5">
       <c r="A29" s="1">
         <v>28</v>
       </c>
@@ -3145,11 +3095,11 @@
       <c r="D29" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="E29" s="4" t="s">
+      <c r="E29" s="1" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="30" ht="14.75" spans="1:5">
+    <row r="30" spans="1:5">
       <c r="A30" s="1">
         <v>29</v>
       </c>
@@ -3162,11 +3112,11 @@
       <c r="D30" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="E30" s="4" t="s">
+      <c r="E30" s="1" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="31" ht="14.75" spans="1:5">
+    <row r="31" spans="1:5">
       <c r="A31" s="1">
         <v>30</v>
       </c>
@@ -3179,11 +3129,11 @@
       <c r="D31" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="E31" s="4" t="s">
+      <c r="E31" s="1" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="32" ht="17.75" spans="1:5">
+    <row r="32" spans="1:5">
       <c r="A32" s="1">
         <v>31</v>
       </c>
@@ -3193,14 +3143,14 @@
       <c r="C32" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="D32" s="5" t="s">
+      <c r="D32" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="E32" s="4" t="s">
+      <c r="E32" s="1" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="33" ht="14.75" spans="1:5">
+    <row r="33" spans="1:5">
       <c r="A33" s="1">
         <v>32</v>
       </c>
@@ -3213,11 +3163,11 @@
       <c r="D33" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="E33" s="4" t="s">
+      <c r="E33" s="1" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="34" ht="14.75" spans="1:5">
+    <row r="34" spans="1:5">
       <c r="A34" s="1">
         <v>33</v>
       </c>
@@ -3230,11 +3180,11 @@
       <c r="D34" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="E34" s="4" t="s">
+      <c r="E34" s="1" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="35" ht="17.75" spans="1:5">
+    <row r="35" spans="1:5">
       <c r="A35" s="1">
         <v>34</v>
       </c>
@@ -3244,14 +3194,14 @@
       <c r="C35" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="D35" s="5" t="s">
+      <c r="D35" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="E35" s="4" t="s">
+      <c r="E35" s="1" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="36" ht="17.75" spans="1:5">
+    <row r="36" spans="1:5">
       <c r="A36" s="1">
         <v>35</v>
       </c>
@@ -3261,14 +3211,14 @@
       <c r="C36" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="D36" s="5" t="s">
+      <c r="D36" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="E36" s="4" t="s">
+      <c r="E36" s="1" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="37" ht="17.75" spans="1:5">
+    <row r="37" spans="1:5">
       <c r="A37" s="1">
         <v>36</v>
       </c>
@@ -3278,14 +3228,14 @@
       <c r="C37" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="D37" s="5" t="s">
+      <c r="D37" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="E37" s="4" t="s">
+      <c r="E37" s="1" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="38" ht="14.75" spans="1:5">
+    <row r="38" spans="1:5">
       <c r="A38" s="1">
         <v>37</v>
       </c>
@@ -3298,11 +3248,11 @@
       <c r="D38" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="E38" s="4" t="s">
+      <c r="E38" s="1" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="39" ht="17.75" spans="1:5">
+    <row r="39" spans="1:5">
       <c r="A39" s="1">
         <v>38</v>
       </c>
@@ -3312,14 +3262,14 @@
       <c r="C39" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="D39" s="5" t="s">
+      <c r="D39" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="E39" s="4" t="s">
+      <c r="E39" s="1" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="40" ht="17.75" spans="1:5">
+    <row r="40" spans="1:5">
       <c r="A40" s="1">
         <v>39</v>
       </c>
@@ -3329,14 +3279,14 @@
       <c r="C40" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="D40" s="5" t="s">
+      <c r="D40" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="E40" s="4" t="s">
+      <c r="E40" s="1" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="41" ht="17.75" spans="1:5">
+    <row r="41" spans="1:5">
       <c r="A41" s="1">
         <v>40</v>
       </c>
@@ -3346,14 +3296,14 @@
       <c r="C41" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="D41" s="5" t="s">
+      <c r="D41" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="E41" s="4" t="s">
+      <c r="E41" s="1" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="42" ht="17.75" spans="1:5">
+    <row r="42" spans="1:5">
       <c r="A42" s="1">
         <v>41</v>
       </c>
@@ -3363,14 +3313,14 @@
       <c r="C42" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="D42" s="5" t="s">
+      <c r="D42" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="E42" s="4" t="s">
+      <c r="E42" s="1" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="43" ht="17.75" spans="1:5">
+    <row r="43" spans="1:5">
       <c r="A43" s="1">
         <v>42</v>
       </c>
@@ -3380,14 +3330,14 @@
       <c r="C43" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="D43" s="5" t="s">
+      <c r="D43" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="E43" s="4" t="s">
+      <c r="E43" s="1" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="44" ht="17.75" spans="1:5">
+    <row r="44" spans="1:5">
       <c r="A44" s="1">
         <v>43</v>
       </c>
@@ -3397,14 +3347,14 @@
       <c r="C44" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="D44" s="5" t="s">
+      <c r="D44" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="E44" s="4" t="s">
+      <c r="E44" s="1" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="45" ht="14.75" spans="1:5">
+    <row r="45" spans="1:5">
       <c r="A45" s="1">
         <v>44</v>
       </c>
@@ -3417,7 +3367,7 @@
       <c r="D45" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="E45" s="4" t="s">
+      <c r="E45" s="1" t="s">
         <v>217</v>
       </c>
     </row>
@@ -3434,13 +3384,15 @@
   <sheetFormatPr defaultColWidth="9.81818181818182" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="9.81818181818182" style="1" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="22.2727272727273" style="1" customWidth="1"/>
-    <col min="3" max="7" width="9.81818181818182" style="1"/>
+    <col min="2" max="2" width="13.7272727272727" style="1" customWidth="1"/>
+    <col min="3" max="4" width="23" style="1" customWidth="1"/>
+    <col min="5" max="5" width="15.1818181818182" style="1" customWidth="1"/>
+    <col min="6" max="7" width="9.81818181818182" style="1"/>
     <col min="8" max="9" width="9.81818181818182" style="2"/>
     <col min="10" max="16384" width="9.81818181818182" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.75" spans="1:9">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>62</v>
       </c>
@@ -3453,23 +3405,23 @@
       <c r="D1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="1" t="s">
         <v>218</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="2" ht="14.75" spans="1:9">
+    <row r="2" spans="1:9">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -3482,23 +3434,23 @@
       <c r="D2" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="1" t="s">
         <v>222</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="1" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="3" ht="17.75" spans="1:9">
+    <row r="3" spans="1:9">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -3508,26 +3460,26 @@
       <c r="C3" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="1" t="s">
         <v>226</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="1" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="4" ht="17.75" spans="1:9">
+    <row r="4" spans="1:9">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -3537,26 +3489,26 @@
       <c r="C4" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="1" t="s">
         <v>229</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="I4" s="1" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="5" ht="17.75" spans="1:9">
+    <row r="5" spans="1:9">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -3566,26 +3518,26 @@
       <c r="C5" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="1" t="s">
         <v>232</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="H5" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="I5" s="1" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="6" ht="17.75" spans="1:9">
+    <row r="6" spans="1:9">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -3595,26 +3547,26 @@
       <c r="C6" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="1" t="s">
         <v>235</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="H6" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="I6" s="2" t="s">
+      <c r="I6" s="1" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="7" ht="17.75" spans="1:9">
+    <row r="7" spans="1:9">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -3624,26 +3576,26 @@
       <c r="C7" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="1" t="s">
         <v>238</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="H7" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="I7" s="2" t="s">
+      <c r="I7" s="1" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="8" ht="17.75" spans="1:9">
+    <row r="8" spans="1:9">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -3653,26 +3605,26 @@
       <c r="C8" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="1" t="s">
         <v>242</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="H8" s="2" t="s">
+      <c r="H8" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="I8" s="2" t="s">
+      <c r="I8" s="1" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="9" ht="17.75" spans="1:9">
+    <row r="9" spans="1:9">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -3682,26 +3634,26 @@
       <c r="C9" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F9" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="G9" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="H9" s="2" t="s">
+      <c r="H9" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="I9" s="2" t="s">
+      <c r="I9" s="1" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="10" ht="17.75" spans="1:9">
+    <row r="10" spans="1:9">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -3711,26 +3663,26 @@
       <c r="C10" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F10" s="1" t="s">
         <v>250</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="H10" s="2" t="s">
+      <c r="H10" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="I10" s="2" t="s">
+      <c r="I10" s="1" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="11" ht="14.75" spans="1:9">
+    <row r="11" spans="1:9">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -3743,23 +3695,23 @@
       <c r="D11" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="F11" s="1" t="s">
         <v>254</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="H11" s="2" t="s">
+      <c r="H11" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="I11" s="2" t="s">
+      <c r="I11" s="1" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="12" ht="17.75" spans="1:9">
+    <row r="12" spans="1:9">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -3769,26 +3721,26 @@
       <c r="C12" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D12" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="F12" s="1" t="s">
         <v>258</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="H12" s="2" t="s">
+      <c r="H12" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="I12" s="2" t="s">
+      <c r="I12" s="1" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="13" ht="17.75" spans="1:9">
+    <row r="13" spans="1:9">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -3798,26 +3750,26 @@
       <c r="C13" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D13" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E13" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="F13" s="4" t="s">
+      <c r="F13" s="1" t="s">
         <v>262</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="H13" s="2" t="s">
+      <c r="H13" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="I13" s="2" t="s">
+      <c r="I13" s="1" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="14" ht="17.75" spans="1:9">
+    <row r="14" spans="1:9">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -3827,26 +3779,26 @@
       <c r="C14" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="F14" s="1" t="s">
         <v>265</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="H14" s="2" t="s">
+      <c r="H14" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="I14" s="2" t="s">
+      <c r="I14" s="1" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="15" ht="17.75" spans="1:9">
+    <row r="15" spans="1:9">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -3856,26 +3808,26 @@
       <c r="C15" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="D15" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="E15" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="F15" s="1" t="s">
         <v>269</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="H15" s="2" t="s">
+      <c r="H15" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="I15" s="2" t="s">
+      <c r="I15" s="1" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="16" ht="14.75" spans="1:9">
+    <row r="16" spans="1:9">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -3888,23 +3840,23 @@
       <c r="D16" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E16" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="F16" s="1" t="s">
         <v>273</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="H16" s="2" t="s">
+      <c r="H16" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="I16" s="2" t="s">
+      <c r="I16" s="1" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="17" ht="14.75" spans="1:9">
+    <row r="17" spans="1:9">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -3917,23 +3869,23 @@
       <c r="D17" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="E17" s="4" t="s">
+      <c r="E17" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="F17" s="4" t="s">
+      <c r="F17" s="1" t="s">
         <v>275</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="H17" s="2" t="s">
+      <c r="H17" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="I17" s="2" t="s">
+      <c r="I17" s="1" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="18" ht="17.75" spans="1:9">
+    <row r="18" spans="1:9">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -3943,26 +3895,26 @@
       <c r="C18" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="D18" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="E18" s="4" t="s">
+      <c r="E18" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="F18" s="4" t="s">
+      <c r="F18" s="1" t="s">
         <v>276</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="H18" s="2" t="s">
+      <c r="H18" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="I18" s="2" t="s">
+      <c r="I18" s="1" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="19" ht="17.75" spans="1:9">
+    <row r="19" spans="1:9">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -3972,26 +3924,26 @@
       <c r="C19" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="D19" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="E19" s="4" t="s">
+      <c r="E19" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="F19" s="4" t="s">
+      <c r="F19" s="1" t="s">
         <v>279</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="H19" s="2" t="s">
+      <c r="H19" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="I19" s="2" t="s">
+      <c r="I19" s="1" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="20" ht="17.75" spans="1:9">
+    <row r="20" spans="1:9">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -4001,26 +3953,26 @@
       <c r="C20" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="D20" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="E20" s="4" t="s">
+      <c r="E20" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="F20" s="4" t="s">
+      <c r="F20" s="1" t="s">
         <v>280</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="H20" s="2" t="s">
+      <c r="H20" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="I20" s="2" t="s">
+      <c r="I20" s="1" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="21" ht="17.75" spans="1:9">
+    <row r="21" spans="1:9">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -4030,26 +3982,26 @@
       <c r="C21" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="D21" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="E21" s="4" t="s">
+      <c r="E21" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="F21" s="4" t="s">
+      <c r="F21" s="1" t="s">
         <v>282</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="H21" s="2" t="s">
+      <c r="H21" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="I21" s="2" t="s">
+      <c r="I21" s="1" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="22" ht="14.75" spans="1:9">
+    <row r="22" spans="1:9">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -4062,23 +4014,23 @@
       <c r="D22" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="E22" s="4" t="s">
+      <c r="E22" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="F22" s="4" t="s">
+      <c r="F22" s="1" t="s">
         <v>285</v>
       </c>
       <c r="G22" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="H22" s="2" t="s">
+      <c r="H22" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="I22" s="2" t="s">
+      <c r="I22" s="1" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="23" ht="17.75" spans="1:9">
+    <row r="23" spans="1:9">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -4088,26 +4040,26 @@
       <c r="C23" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="D23" s="5" t="s">
+      <c r="D23" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="E23" s="4" t="s">
+      <c r="E23" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F23" s="4" t="s">
+      <c r="F23" s="1" t="s">
         <v>287</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="H23" s="2" t="s">
+      <c r="H23" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="I23" s="2" t="s">
+      <c r="I23" s="1" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="24" ht="14.75" spans="1:9">
+    <row r="24" spans="1:9">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -4117,26 +4069,26 @@
       <c r="C24" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="D24" s="6" t="s">
+      <c r="D24" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="E24" s="4" t="s">
+      <c r="E24" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="F24" s="4" t="s">
+      <c r="F24" s="1" t="s">
         <v>290</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="H24" s="2" t="s">
+      <c r="H24" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="I24" s="2" t="s">
+      <c r="I24" s="1" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="25" ht="17.75" spans="1:9">
+    <row r="25" spans="1:9">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -4146,26 +4098,26 @@
       <c r="C25" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="D25" s="5" t="s">
+      <c r="D25" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="E25" s="4" t="s">
+      <c r="E25" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="F25" s="4" t="s">
+      <c r="F25" s="1" t="s">
         <v>293</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="H25" s="2" t="s">
+      <c r="H25" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="I25" s="2" t="s">
+      <c r="I25" s="1" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="26" ht="17.75" spans="1:9">
+    <row r="26" spans="1:9">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -4175,26 +4127,26 @@
       <c r="C26" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="D26" s="5" t="s">
+      <c r="D26" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="E26" s="4" t="s">
+      <c r="E26" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="F26" s="4" t="s">
+      <c r="F26" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="G26" s="4" t="s">
+      <c r="G26" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="H26" s="2" t="s">
+      <c r="H26" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="I26" s="2" t="s">
+      <c r="I26" s="1" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="27" ht="14.75" spans="1:9">
+    <row r="27" spans="1:9">
       <c r="A27" s="1">
         <v>26</v>
       </c>
@@ -4204,26 +4156,26 @@
       <c r="C27" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="D27" s="6" t="s">
+      <c r="D27" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="E27" s="4" t="s">
+      <c r="E27" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="F27" s="4" t="s">
+      <c r="F27" s="1" t="s">
         <v>298</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="H27" s="2" t="s">
+      <c r="H27" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="I27" s="2" t="s">
+      <c r="I27" s="1" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="28" ht="14.75" spans="1:9">
+    <row r="28" spans="1:9">
       <c r="A28" s="1">
         <v>27</v>
       </c>
@@ -4236,23 +4188,23 @@
       <c r="D28" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="E28" s="4" t="s">
+      <c r="E28" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="F28" s="4" t="s">
+      <c r="F28" s="1" t="s">
         <v>301</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="H28" s="2" t="s">
+      <c r="H28" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="I28" s="2" t="s">
+      <c r="I28" s="1" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="29" ht="14.75" spans="1:9">
+    <row r="29" spans="1:9">
       <c r="A29" s="1">
         <v>28</v>
       </c>
@@ -4265,23 +4217,23 @@
       <c r="D29" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="E29" s="4" t="s">
+      <c r="E29" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="F29" s="4" t="s">
+      <c r="F29" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="G29" s="4" t="s">
+      <c r="G29" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="H29" s="2" t="s">
+      <c r="H29" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="I29" s="2" t="s">
+      <c r="I29" s="1" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="30" ht="14.75" spans="1:9">
+    <row r="30" spans="1:9">
       <c r="A30" s="1">
         <v>29</v>
       </c>
@@ -4294,23 +4246,23 @@
       <c r="D30" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="E30" s="4" t="s">
+      <c r="E30" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F30" s="4" t="s">
+      <c r="F30" s="1" t="s">
         <v>306</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="H30" s="2" t="s">
+      <c r="H30" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="I30" s="2" t="s">
+      <c r="I30" s="1" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="31" ht="14.75" spans="1:9">
+    <row r="31" spans="1:9">
       <c r="A31" s="1">
         <v>30</v>
       </c>
@@ -4323,23 +4275,23 @@
       <c r="D31" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="E31" s="4" t="s">
+      <c r="E31" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="F31" s="4" t="s">
+      <c r="F31" s="1" t="s">
         <v>308</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="H31" s="2" t="s">
+      <c r="H31" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="I31" s="2" t="s">
+      <c r="I31" s="1" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="32" ht="17.75" spans="1:9">
+    <row r="32" spans="1:9">
       <c r="A32" s="1">
         <v>31</v>
       </c>
@@ -4349,26 +4301,26 @@
       <c r="C32" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="D32" s="5" t="s">
+      <c r="D32" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="E32" s="4" t="s">
+      <c r="E32" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="F32" s="4" t="s">
+      <c r="F32" s="1" t="s">
         <v>311</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="H32" s="2" t="s">
+      <c r="H32" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="I32" s="2" t="s">
+      <c r="I32" s="1" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="33" ht="14.75" spans="1:9">
+    <row r="33" spans="1:9">
       <c r="A33" s="1">
         <v>32</v>
       </c>
@@ -4381,23 +4333,23 @@
       <c r="D33" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="E33" s="4" t="s">
+      <c r="E33" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="F33" s="4" t="s">
+      <c r="F33" s="1" t="s">
         <v>315</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="H33" s="2" t="s">
+      <c r="H33" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="I33" s="2" t="s">
+      <c r="I33" s="1" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="34" ht="14.75" spans="1:9">
+    <row r="34" spans="1:9">
       <c r="A34" s="1">
         <v>33</v>
       </c>
@@ -4410,23 +4362,23 @@
       <c r="D34" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="E34" s="4" t="s">
+      <c r="E34" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="F34" s="4" t="s">
+      <c r="F34" s="1" t="s">
         <v>318</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="H34" s="2" t="s">
+      <c r="H34" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="I34" s="2" t="s">
+      <c r="I34" s="1" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="35" ht="17.75" spans="1:9">
+    <row r="35" spans="1:9">
       <c r="A35" s="1">
         <v>34</v>
       </c>
@@ -4436,26 +4388,26 @@
       <c r="C35" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="D35" s="5" t="s">
+      <c r="D35" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="E35" s="4" t="s">
+      <c r="E35" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="F35" s="4" t="s">
+      <c r="F35" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="G35" s="4" t="s">
+      <c r="G35" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="H35" s="2" t="s">
+      <c r="H35" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="I35" s="2" t="s">
+      <c r="I35" s="1" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="36" ht="17.75" spans="1:9">
+    <row r="36" spans="1:9">
       <c r="A36" s="1">
         <v>35</v>
       </c>
@@ -4465,26 +4417,26 @@
       <c r="C36" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="D36" s="5" t="s">
+      <c r="D36" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="E36" s="4" t="s">
+      <c r="E36" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="F36" s="4" t="s">
+      <c r="F36" s="1" t="s">
         <v>325</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="H36" s="2" t="s">
+      <c r="H36" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="I36" s="2" t="s">
+      <c r="I36" s="1" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="37" ht="17.75" spans="1:9">
+    <row r="37" spans="1:9">
       <c r="A37" s="1">
         <v>36</v>
       </c>
@@ -4494,26 +4446,26 @@
       <c r="C37" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="D37" s="5" t="s">
+      <c r="D37" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="E37" s="4" t="s">
+      <c r="E37" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="F37" s="4" t="s">
+      <c r="F37" s="1" t="s">
         <v>327</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="H37" s="2" t="s">
+      <c r="H37" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="I37" s="2" t="s">
+      <c r="I37" s="1" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="38" ht="14.75" spans="1:9">
+    <row r="38" spans="1:9">
       <c r="A38" s="1">
         <v>37</v>
       </c>
@@ -4526,23 +4478,23 @@
       <c r="D38" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="E38" s="4" t="s">
+      <c r="E38" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="F38" s="4" t="s">
+      <c r="F38" s="1" t="s">
         <v>276</v>
       </c>
       <c r="G38" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="H38" s="2" t="s">
+      <c r="H38" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="I38" s="2" t="s">
+      <c r="I38" s="1" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="39" ht="17.75" spans="1:9">
+    <row r="39" spans="1:9">
       <c r="A39" s="1">
         <v>38</v>
       </c>
@@ -4552,26 +4504,26 @@
       <c r="C39" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="D39" s="5" t="s">
+      <c r="D39" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="E39" s="4" t="s">
+      <c r="E39" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="F39" s="4" t="s">
+      <c r="F39" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="G39" s="4" t="s">
+      <c r="G39" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="H39" s="2" t="s">
+      <c r="H39" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="I39" s="2" t="s">
+      <c r="I39" s="1" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="40" ht="17.75" spans="1:9">
+    <row r="40" spans="1:9">
       <c r="A40" s="1">
         <v>39</v>
       </c>
@@ -4581,26 +4533,26 @@
       <c r="C40" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="D40" s="5" t="s">
+      <c r="D40" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="E40" s="4" t="s">
+      <c r="E40" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="F40" s="4" t="s">
+      <c r="F40" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="G40" s="4" t="s">
+      <c r="G40" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="H40" s="2" t="s">
+      <c r="H40" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="I40" s="2" t="s">
+      <c r="I40" s="1" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="41" ht="17.75" spans="1:9">
+    <row r="41" spans="1:9">
       <c r="A41" s="1">
         <v>40</v>
       </c>
@@ -4610,26 +4562,26 @@
       <c r="C41" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="D41" s="5" t="s">
+      <c r="D41" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="E41" s="4" t="s">
+      <c r="E41" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="F41" s="4" t="s">
+      <c r="F41" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="G41" s="4" t="s">
+      <c r="G41" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="H41" s="2" t="s">
+      <c r="H41" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="I41" s="2" t="s">
+      <c r="I41" s="1" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="42" ht="17.75" spans="1:9">
+    <row r="42" spans="1:9">
       <c r="A42" s="1">
         <v>41</v>
       </c>
@@ -4639,26 +4591,26 @@
       <c r="C42" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="D42" s="5" t="s">
+      <c r="D42" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="E42" s="4" t="s">
+      <c r="E42" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="F42" s="4" t="s">
+      <c r="F42" s="1" t="s">
         <v>342</v>
       </c>
       <c r="G42" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="H42" s="2" t="s">
+      <c r="H42" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="I42" s="2" t="s">
+      <c r="I42" s="1" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="43" ht="17.75" spans="1:9">
+    <row r="43" spans="1:9">
       <c r="A43" s="1">
         <v>42</v>
       </c>
@@ -4668,26 +4620,26 @@
       <c r="C43" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="D43" s="5" t="s">
+      <c r="D43" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="E43" s="4" t="s">
+      <c r="E43" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="F43" s="4" t="s">
+      <c r="F43" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="G43" s="4" t="s">
+      <c r="G43" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="H43" s="2" t="s">
+      <c r="H43" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="I43" s="2" t="s">
+      <c r="I43" s="1" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="44" ht="17.75" spans="1:9">
+    <row r="44" spans="1:9">
       <c r="A44" s="1">
         <v>43</v>
       </c>
@@ -4697,26 +4649,26 @@
       <c r="C44" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="D44" s="5" t="s">
+      <c r="D44" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="E44" s="4" t="s">
+      <c r="E44" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="F44" s="4" t="s">
+      <c r="F44" s="1" t="s">
         <v>347</v>
       </c>
       <c r="G44" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="H44" s="2" t="s">
+      <c r="H44" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="I44" s="2" t="s">
+      <c r="I44" s="1" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="45" ht="14.75" spans="1:9">
+    <row r="45" spans="1:9">
       <c r="A45" s="1">
         <v>44</v>
       </c>
@@ -4729,19 +4681,19 @@
       <c r="D45" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="E45" s="4" t="s">
+      <c r="E45" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="F45" s="4" t="s">
+      <c r="F45" s="1" t="s">
         <v>349</v>
       </c>
       <c r="G45" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="H45" s="2" t="s">
+      <c r="H45" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="I45" s="2" t="s">
+      <c r="I45" s="1" t="s">
         <v>225</v>
       </c>
     </row>
